--- a/output/pdf_financials_xlsx/PGE.xlsx
+++ b/output/pdf_financials_xlsx/PGE.xlsx
@@ -1276,16 +1276,16 @@
         <v>-0.520489</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.518313</v>
+        <v>-0.518313</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.421523</v>
+        <v>-0.421523</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.124767</v>
@@ -1331,7 +1331,7 @@
         <v>0.193112</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1.670011</v>
+        <v>-0.629033</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1573,19 +1573,19 @@
         <v>-0.626126</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.149522</v>
+        <v>-1.149522</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.518313</v>
+        <v>-0.518313</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.421523</v>
+        <v>-0.421523</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.124767</v>
@@ -1747,19 +1747,19 @@
         <v>-0.626126</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.149522</v>
+        <v>-1.149522</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.518313</v>
+        <v>-0.518313</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.421523</v>
+        <v>-0.421523</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.124767</v>
@@ -1923,19 +1923,19 @@
         <v>31.3063</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>57.4761</v>
+        <v>-57.4761</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>7.887691</v>
+        <v>-7.887691</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>9.874000000000001</v>
+        <v>-9.874000000000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.957825</v>
+        <v>-12.957825</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>14.050767</v>
+        <v>-14.050767</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1986,16 +1986,16 @@
         <v>-0.520489</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.518313</v>
+        <v>-0.518313</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.421523</v>
+        <v>-0.421523</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.124767</v>
@@ -2102,16 +2102,16 @@
         <v>-0.520489</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.518313</v>
+        <v>-0.518313</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.421523</v>
+        <v>-0.421523</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.124767</v>
@@ -2249,19 +2249,19 @@
         <v>-23.57214875286547</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-320.8542351519437</v>
+        <v>-120.8542351519436</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -5886,49 +5886,49 @@
         <v>0.521937</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.623308</v>
+        <v>0.382476</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.610993</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.329405</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.329405</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.120786</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.051886</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.029334</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.434575</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.6193070000000001</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.851899</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.523297</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.174863</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.828222</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.767625</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.481662</v>
       </c>
     </row>
     <row r="93">
@@ -9800,7 +9800,11 @@
           <t>Share-based payment reserve 9f</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10384,7 +10388,11 @@
           <t>Share-based payment reserve 8f</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10574,7 +10582,11 @@
           <t>Share-based payment reserve 8g</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12685,7 +12697,11 @@
           <t>Share-based payment reserve 8(e)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13475,7 +13491,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -14188,7 +14208,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -16939,7 +16963,11 @@
           <t>Share-based payments reserve 120,786</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -19486,7 +19514,11 @@
           <t>Share-based payments reserve 245,348</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -20698,7 +20730,11 @@
           <t>Share‐based payments reserve</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -22318,7 +22354,11 @@
           <t>Share-based payment reserve 610,993</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -56874,13 +56914,13 @@
         </is>
       </c>
       <c r="I485" s="5" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="J485" s="5" t="n">
-        <v>0.518313</v>
+        <v>-0.518313</v>
       </c>
       <c r="K485" s="5" t="n">
-        <v>0.421523</v>
+        <v>-0.421523</v>
       </c>
       <c r="L485" t="inlineStr">
         <is>
@@ -58077,10 +58117,10 @@
         </is>
       </c>
       <c r="H497" s="5" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="I497" s="5" t="n">
-        <v>0.4937</v>
+        <v>-0.4937</v>
       </c>
       <c r="J497" t="inlineStr">
         <is>
@@ -59082,10 +59122,10 @@
         </is>
       </c>
       <c r="G507" s="5" t="n">
-        <v>1.149522</v>
+        <v>-1.149522</v>
       </c>
       <c r="H507" s="5" t="n">
-        <v>1.735292</v>
+        <v>-1.735292</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PGE.xlsx
+++ b/output/pdf_financials_xlsx/PGE.xlsx
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002841</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002181</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000112</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-3e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1071,19 +1071,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.022191</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.009828999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.009858</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.030624</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.026559</v>
       </c>
     </row>
     <row r="13">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>7.995333</v>
+        <v>7.392937</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>34.730125</v>
+        <v>39.286968</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>51.28668</v>
+        <v>51.572019</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>92.00239999999999</v>
@@ -1983,16 +1983,16 @@
         <v>-0.819238</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.520489</v>
+        <v>-0.517648</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.735292</v>
+        <v>-1.733111</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.4937</v>
+        <v>-0.493588</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.518313</v>
+        <v>-0.518283</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.421523</v>
@@ -2013,19 +2013,19 @@
         <v>-3.680096</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.572174</v>
+        <v>-5.594365</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.259092</v>
+        <v>-7.268921</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.306554</v>
+        <v>-4.316412</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.529304</v>
+        <v>-5.559928</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.788071</v>
+        <v>-3.81463</v>
       </c>
     </row>
     <row r="28">
@@ -2099,16 +2099,16 @@
         <v>-0.819238</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.520489</v>
+        <v>-0.517648</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.735292</v>
+        <v>-1.733111</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.4937</v>
+        <v>-0.493588</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.518313</v>
+        <v>-0.518283</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.421523</v>
@@ -2129,19 +2129,19 @@
         <v>-3.680096</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.572174</v>
+        <v>-5.594365</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.259092</v>
+        <v>-7.268921</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.306554</v>
+        <v>-4.316412</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.529304</v>
+        <v>-5.559928</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.788071</v>
+        <v>-3.81463</v>
       </c>
     </row>
     <row r="30">
@@ -2400,37 +2400,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.103616</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.442956</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.442956</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.350986</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007798</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.009185</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005618</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.5475950000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.27024</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.048427</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>2.261726</v>
@@ -2439,16 +2439,16 @@
         <v>2.509404</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.401965</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.027387</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.149404</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.239467</v>
       </c>
     </row>
     <row r="35">
@@ -2516,37 +2516,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.103616</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.442956</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.442956</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.350986</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007798</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.009185</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005618</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.5475950000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.27024</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.048427</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>2.261726</v>
@@ -2555,16 +2555,16 @@
         <v>2.509404</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.401965</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.027387</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.149404</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.239467</v>
       </c>
     </row>
     <row r="37">
@@ -3212,28 +3212,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.110499</v>
+        <v>0.006883</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.507954</v>
+        <v>0.064998</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.507954</v>
+        <v>0.064998</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.053305</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.039293</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.039293</v>
+        <v>0.031495</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.012337</v>
+        <v>0.003152</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.005618</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3251,16 +3251,16 @@
         <v>0.694344</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.231356</v>
+        <v>0.829391</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.402279</v>
+        <v>1.374892</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.320222</v>
+        <v>1.170818</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.834819</v>
+        <v>1.595352</v>
       </c>
     </row>
     <row r="49">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -19098,7 +19098,11 @@
           <t>Reclamation deposits 7 3,000</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -20219,7 +20223,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -21437,7 +21445,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -21843,7 +21851,11 @@
           <t>Reclamation deposits 5 23,000</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -22764,7 +22776,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -23168,7 +23180,11 @@
           <t>Reclamation Deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -24176,7 +24192,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -24376,7 +24392,11 @@
           <t>Reclamation Deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>0.02</v>
       </c>
@@ -38269,7 +38289,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -39871,7 +39895,11 @@
           <t>Reclamation Deposits</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E314" s="5" t="n">
         <v>-0.016</v>
       </c>
@@ -41500,7 +41528,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -50161,7 +50189,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -52585,7 +52613,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -56688,7 +56716,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -57896,7 +57924,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
